--- a/assets/infobasica/planilhas/aula06_nivel3.xlsx
+++ b/assets/infobasica/planilhas/aula06_nivel3.xlsx
@@ -536,7 +536,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Conta de energia: leitura anterior em B1, atual em B2, preço do kWh em B3, taxa fixa em B4; consumo =B2-B1 e valor =ARRED((B2-B1)B3+B4; 2).</t>
+          <t>Conta de energia: leitura anterior em B1, atual em B2, preço do kWh em B3, taxa fixa em B4; consumo =B2-B1 e valor =ARRED((B2-B1)*B3+B4; 2).</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Para abrir no Google Planilhas: Google Drive → Novo → Upload de arquivo; depois clique no arquivo → Abrir com → Planilhas Google.</t>
+          <t>Esta é a sua cópia: altere à vontade.</t>
         </is>
       </c>
     </row>
